--- a/3-Project_Planning/1-RBS/PrimeAI_RBS_Menu_Mapping_v2.1.xlsx
+++ b/3-Project_Planning/1-RBS/PrimeAI_RBS_Menu_Mapping_v2.1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bkwork/WorkFolder/1-Development/1-Working/0-Dev_Status/0-Created_by_Claude/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bkwork/WorkFolder/1-Development/0-Git_Work/prime-ai_db/databases/3-Project_Planning/1-RBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E515467-2148-754B-B299-F40F335DEBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F196DE-9639-E448-B13C-ABA4C397435B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 How To Read" sheetId="1" r:id="rId1"/>
@@ -5013,10 +5013,22 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -5049,29 +5061,17 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5395,7 +5395,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="48"/>
@@ -5407,7 +5407,7 @@
       <c r="H1" s="48"/>
     </row>
     <row r="2" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="59" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="48"/>
@@ -5487,7 +5487,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="61" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="48"/>
@@ -5499,92 +5499,92 @@
       <c r="H10" s="48"/>
     </row>
     <row r="11" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="60" t="s">
+      <c r="B11" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="51"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="55"/>
     </row>
     <row r="12" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="56" t="s">
+      <c r="B12" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="51"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="55"/>
     </row>
     <row r="13" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="54" t="s">
+      <c r="B13" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="51"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="55"/>
     </row>
     <row r="14" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="49" t="s">
+      <c r="B14" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="51"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="55"/>
     </row>
     <row r="15" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="59" t="s">
+      <c r="B15" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="51"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="55"/>
     </row>
     <row r="16" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="51"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="55"/>
     </row>
     <row r="17" spans="2:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="50"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="51"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="55"/>
     </row>
     <row r="18" spans="2:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="53" t="s">
+      <c r="B18" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="51"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -5617,16 +5617,16 @@
     <col min="6" max="6" width="6" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="43.33203125" customWidth="1"/>
-    <col min="10" max="10" width="34" customWidth="1"/>
-    <col min="11" max="11" width="60" customWidth="1"/>
+    <col min="9" max="9" width="36" customWidth="1"/>
+    <col min="10" max="10" width="43" customWidth="1"/>
+    <col min="11" max="11" width="65.83203125" customWidth="1"/>
     <col min="12" max="12" width="28" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>31</v>
       </c>
       <c r="B1" s="48"/>
@@ -5688,7 +5688,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="68" t="s">
         <v>45</v>
       </c>
       <c r="B3" s="48"/>
@@ -5707,7 +5707,7 @@
     </row>
     <row r="4" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7"/>
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="66" t="s">
         <v>46</v>
       </c>
       <c r="C4" s="48"/>
@@ -5930,7 +5930,7 @@
     </row>
     <row r="13" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
-      <c r="B13" s="63" t="s">
+      <c r="B13" s="66" t="s">
         <v>68</v>
       </c>
       <c r="C13" s="48"/>
@@ -5949,7 +5949,7 @@
     <row r="14" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="22"/>
       <c r="B14" s="22"/>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="67" t="s">
         <v>69</v>
       </c>
       <c r="D14" s="48"/>
@@ -6419,7 +6419,7 @@
     <row r="32" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="22"/>
       <c r="B32" s="22"/>
-      <c r="C32" s="61" t="s">
+      <c r="C32" s="67" t="s">
         <v>107</v>
       </c>
       <c r="D32" s="48"/>
@@ -6889,7 +6889,7 @@
     <row r="50" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="22"/>
       <c r="B50" s="22"/>
-      <c r="C50" s="61" t="s">
+      <c r="C50" s="67" t="s">
         <v>111</v>
       </c>
       <c r="D50" s="48"/>
@@ -7359,7 +7359,7 @@
     <row r="68" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="22"/>
       <c r="B68" s="22"/>
-      <c r="C68" s="61" t="s">
+      <c r="C68" s="67" t="s">
         <v>115</v>
       </c>
       <c r="D68" s="48"/>
@@ -7829,7 +7829,7 @@
     <row r="86" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="22"/>
       <c r="B86" s="22"/>
-      <c r="C86" s="61" t="s">
+      <c r="C86" s="67" t="s">
         <v>119</v>
       </c>
       <c r="D86" s="48"/>
@@ -8052,7 +8052,7 @@
     </row>
     <row r="95" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="7"/>
-      <c r="B95" s="63" t="s">
+      <c r="B95" s="66" t="s">
         <v>138</v>
       </c>
       <c r="C95" s="48"/>
@@ -8972,7 +8972,7 @@
     </row>
     <row r="130" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="7"/>
-      <c r="B130" s="63" t="s">
+      <c r="B130" s="66" t="s">
         <v>145</v>
       </c>
       <c r="C130" s="48"/>
@@ -10793,7 +10793,7 @@
       </c>
     </row>
     <row r="199" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="62" t="s">
+      <c r="A199" s="68" t="s">
         <v>158</v>
       </c>
       <c r="B199" s="48"/>
@@ -10812,7 +10812,7 @@
     </row>
     <row r="200" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="7"/>
-      <c r="B200" s="63" t="s">
+      <c r="B200" s="66" t="s">
         <v>159</v>
       </c>
       <c r="C200" s="48"/>
@@ -12133,7 +12133,7 @@
     </row>
     <row r="250" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="7"/>
-      <c r="B250" s="63" t="s">
+      <c r="B250" s="66" t="s">
         <v>265</v>
       </c>
       <c r="C250" s="48"/>
@@ -13053,7 +13053,7 @@
     </row>
     <row r="285" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="7"/>
-      <c r="B285" s="63" t="s">
+      <c r="B285" s="66" t="s">
         <v>272</v>
       </c>
       <c r="C285" s="48"/>
@@ -15325,7 +15325,7 @@
       </c>
     </row>
     <row r="371" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A371" s="62" t="s">
+      <c r="A371" s="68" t="s">
         <v>322</v>
       </c>
       <c r="B371" s="48"/>
@@ -15344,7 +15344,7 @@
     </row>
     <row r="372" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="7"/>
-      <c r="B372" s="63" t="s">
+      <c r="B372" s="66" t="s">
         <v>323</v>
       </c>
       <c r="C372" s="48"/>
@@ -18723,7 +18723,7 @@
     </row>
     <row r="501" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A501" s="7"/>
-      <c r="B501" s="63" t="s">
+      <c r="B501" s="66" t="s">
         <v>406</v>
       </c>
       <c r="C501" s="48"/>
@@ -21516,6 +21516,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A199:N199"/>
+    <mergeCell ref="C68:N68"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="B372:N372"/>
     <mergeCell ref="B130:N130"/>
@@ -21532,8 +21534,6 @@
     <mergeCell ref="B250:N250"/>
     <mergeCell ref="B13:N13"/>
     <mergeCell ref="C14:N14"/>
-    <mergeCell ref="A199:N199"/>
-    <mergeCell ref="C68:N68"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21552,16 +21552,16 @@
     <col min="6" max="6" width="6" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="31" customWidth="1"/>
-    <col min="10" max="10" width="27.1640625" customWidth="1"/>
-    <col min="11" max="11" width="60" customWidth="1"/>
-    <col min="12" max="12" width="28" customWidth="1"/>
+    <col min="9" max="9" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="51" t="s">
         <v>478</v>
       </c>
       <c r="B1" s="48"/>
@@ -21623,7 +21623,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="50" t="s">
         <v>479</v>
       </c>
       <c r="B3" s="48"/>
@@ -21642,7 +21642,7 @@
     </row>
     <row r="4" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="24"/>
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="47" t="s">
         <v>480</v>
       </c>
       <c r="C4" s="48"/>
@@ -22448,7 +22448,7 @@
     </row>
     <row r="35" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="24"/>
-      <c r="B35" s="66" t="s">
+      <c r="B35" s="47" t="s">
         <v>265</v>
       </c>
       <c r="C35" s="48"/>
@@ -23368,7 +23368,7 @@
     </row>
     <row r="70" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="24"/>
-      <c r="B70" s="66" t="s">
+      <c r="B70" s="47" t="s">
         <v>488</v>
       </c>
       <c r="C70" s="48"/>
@@ -24738,7 +24738,7 @@
       </c>
     </row>
     <row r="122" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="67" t="s">
+      <c r="A122" s="50" t="s">
         <v>498</v>
       </c>
       <c r="B122" s="48"/>
@@ -24757,7 +24757,7 @@
     </row>
     <row r="123" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="24"/>
-      <c r="B123" s="66" t="s">
+      <c r="B123" s="47" t="s">
         <v>499</v>
       </c>
       <c r="C123" s="48"/>
@@ -24776,7 +24776,7 @@
     <row r="124" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="30"/>
       <c r="B124" s="30"/>
-      <c r="C124" s="65" t="s">
+      <c r="C124" s="49" t="s">
         <v>500</v>
       </c>
       <c r="D124" s="48"/>
@@ -25630,7 +25630,7 @@
     <row r="157" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="30"/>
       <c r="B157" s="30"/>
-      <c r="C157" s="65" t="s">
+      <c r="C157" s="49" t="s">
         <v>537</v>
       </c>
       <c r="D157" s="48"/>
@@ -25982,7 +25982,7 @@
     <row r="171" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="30"/>
       <c r="B171" s="30"/>
-      <c r="C171" s="65" t="s">
+      <c r="C171" s="49" t="s">
         <v>565</v>
       </c>
       <c r="D171" s="48"/>
@@ -26672,7 +26672,7 @@
     <row r="198" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="30"/>
       <c r="B198" s="30"/>
-      <c r="C198" s="65" t="s">
+      <c r="C198" s="49" t="s">
         <v>595</v>
       </c>
       <c r="D198" s="48"/>
@@ -28229,7 +28229,7 @@
     </row>
     <row r="259" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="24"/>
-      <c r="B259" s="66" t="s">
+      <c r="B259" s="47" t="s">
         <v>632</v>
       </c>
       <c r="C259" s="48"/>
@@ -28248,7 +28248,7 @@
     <row r="260" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="30"/>
       <c r="B260" s="30"/>
-      <c r="C260" s="65" t="s">
+      <c r="C260" s="49" t="s">
         <v>633</v>
       </c>
       <c r="D260" s="48"/>
@@ -29618,7 +29618,7 @@
     <row r="312" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="30"/>
       <c r="B312" s="30"/>
-      <c r="C312" s="65" t="s">
+      <c r="C312" s="49" t="s">
         <v>638</v>
       </c>
       <c r="D312" s="48"/>
@@ -30792,7 +30792,7 @@
       </c>
     </row>
     <row r="358" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A358" s="67" t="s">
+      <c r="A358" s="50" t="s">
         <v>645</v>
       </c>
       <c r="B358" s="48"/>
@@ -30811,7 +30811,7 @@
     </row>
     <row r="359" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="24"/>
-      <c r="B359" s="66" t="s">
+      <c r="B359" s="47" t="s">
         <v>646</v>
       </c>
       <c r="C359" s="48"/>
@@ -30830,7 +30830,7 @@
     <row r="360" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="30"/>
       <c r="B360" s="30"/>
-      <c r="C360" s="65" t="s">
+      <c r="C360" s="49" t="s">
         <v>647</v>
       </c>
       <c r="D360" s="48"/>
@@ -32388,7 +32388,7 @@
     <row r="421" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="30"/>
       <c r="B421" s="30"/>
-      <c r="C421" s="65" t="s">
+      <c r="C421" s="49" t="s">
         <v>685</v>
       </c>
       <c r="D421" s="48"/>
@@ -35107,7 +35107,7 @@
     </row>
     <row r="527" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A527" s="24"/>
-      <c r="B527" s="66" t="s">
+      <c r="B527" s="47" t="s">
         <v>700</v>
       </c>
       <c r="C527" s="48"/>
@@ -35126,7 +35126,7 @@
     <row r="528" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A528" s="30"/>
       <c r="B528" s="30"/>
-      <c r="C528" s="65" t="s">
+      <c r="C528" s="49" t="s">
         <v>701</v>
       </c>
       <c r="D528" s="48"/>
@@ -36918,7 +36918,7 @@
       </c>
     </row>
     <row r="598" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A598" s="67" t="s">
+      <c r="A598" s="50" t="s">
         <v>804</v>
       </c>
       <c r="B598" s="48"/>
@@ -36937,7 +36937,7 @@
     </row>
     <row r="599" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A599" s="24"/>
-      <c r="B599" s="66" t="s">
+      <c r="B599" s="47" t="s">
         <v>805</v>
       </c>
       <c r="C599" s="48"/>
@@ -36956,7 +36956,7 @@
     <row r="600" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A600" s="30"/>
       <c r="B600" s="30"/>
-      <c r="C600" s="65" t="s">
+      <c r="C600" s="49" t="s">
         <v>806</v>
       </c>
       <c r="D600" s="48"/>
@@ -37654,7 +37654,7 @@
       </c>
     </row>
     <row r="628" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A628" s="67" t="s">
+      <c r="A628" s="50" t="s">
         <v>862</v>
       </c>
       <c r="B628" s="48"/>
@@ -37673,7 +37673,7 @@
     </row>
     <row r="629" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A629" s="24"/>
-      <c r="B629" s="66" t="s">
+      <c r="B629" s="47" t="s">
         <v>863</v>
       </c>
       <c r="C629" s="48"/>
@@ -37692,7 +37692,7 @@
     <row r="630" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A630" s="30"/>
       <c r="B630" s="30"/>
-      <c r="C630" s="65" t="s">
+      <c r="C630" s="49" t="s">
         <v>864</v>
       </c>
       <c r="D630" s="48"/>
@@ -40004,7 +40004,7 @@
     <row r="721" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A721" s="30"/>
       <c r="B721" s="30"/>
-      <c r="C721" s="65" t="s">
+      <c r="C721" s="49" t="s">
         <v>962</v>
       </c>
       <c r="D721" s="48"/>
@@ -42382,7 +42382,7 @@
     <row r="815" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A815" s="30"/>
       <c r="B815" s="30"/>
-      <c r="C815" s="65" t="s">
+      <c r="C815" s="49" t="s">
         <v>1011</v>
       </c>
       <c r="D815" s="48"/>
@@ -42840,7 +42840,7 @@
     <row r="834" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A834" s="30"/>
       <c r="B834" s="30"/>
-      <c r="C834" s="65" t="s">
+      <c r="C834" s="49" t="s">
         <v>1016</v>
       </c>
       <c r="D834" s="48"/>
@@ -43518,7 +43518,7 @@
     <row r="862" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A862" s="30"/>
       <c r="B862" s="30"/>
-      <c r="C862" s="65" t="s">
+      <c r="C862" s="49" t="s">
         <v>1023</v>
       </c>
       <c r="D862" s="48"/>
@@ -44618,7 +44618,7 @@
     <row r="907" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A907" s="30"/>
       <c r="B907" s="30"/>
-      <c r="C907" s="65" t="s">
+      <c r="C907" s="49" t="s">
         <v>1049</v>
       </c>
       <c r="D907" s="48"/>
@@ -45156,7 +45156,7 @@
       </c>
     </row>
     <row r="929" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A929" s="67" t="s">
+      <c r="A929" s="50" t="s">
         <v>1094</v>
       </c>
       <c r="B929" s="48"/>
@@ -45175,7 +45175,7 @@
     </row>
     <row r="930" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A930" s="24"/>
-      <c r="B930" s="66" t="s">
+      <c r="B930" s="47" t="s">
         <v>1095</v>
       </c>
       <c r="C930" s="48"/>
@@ -46999,7 +46999,7 @@
     </row>
     <row r="1003" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1003" s="24"/>
-      <c r="B1003" s="66" t="s">
+      <c r="B1003" s="47" t="s">
         <v>1125</v>
       </c>
       <c r="C1003" s="48"/>
@@ -47018,7 +47018,7 @@
     <row r="1004" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1004" s="30"/>
       <c r="B1004" s="30"/>
-      <c r="C1004" s="65" t="s">
+      <c r="C1004" s="49" t="s">
         <v>1126</v>
       </c>
       <c r="D1004" s="48"/>
@@ -48276,7 +48276,7 @@
       </c>
     </row>
     <row r="1053" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1053" s="67" t="s">
+      <c r="A1053" s="50" t="s">
         <v>1161</v>
       </c>
       <c r="B1053" s="48"/>
@@ -48295,7 +48295,7 @@
     </row>
     <row r="1054" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1054" s="24"/>
-      <c r="B1054" s="66" t="s">
+      <c r="B1054" s="47" t="s">
         <v>1162</v>
       </c>
       <c r="C1054" s="48"/>
@@ -50143,7 +50143,7 @@
     </row>
     <row r="1127" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1127" s="24"/>
-      <c r="B1127" s="66" t="s">
+      <c r="B1127" s="47" t="s">
         <v>1205</v>
       </c>
       <c r="C1127" s="48"/>
@@ -50162,7 +50162,7 @@
     <row r="1128" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1128" s="30"/>
       <c r="B1128" s="30"/>
-      <c r="C1128" s="65" t="s">
+      <c r="C1128" s="49" t="s">
         <v>119</v>
       </c>
       <c r="D1128" s="48"/>
@@ -50385,7 +50385,7 @@
     </row>
     <row r="1137" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1137" s="24"/>
-      <c r="B1137" s="66" t="s">
+      <c r="B1137" s="47" t="s">
         <v>1207</v>
       </c>
       <c r="C1137" s="48"/>
@@ -50702,6 +50702,30 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="B1127:N1127"/>
+    <mergeCell ref="A358:N358"/>
+    <mergeCell ref="C198:N198"/>
+    <mergeCell ref="B359:N359"/>
+    <mergeCell ref="A929:N929"/>
+    <mergeCell ref="C1004:N1004"/>
+    <mergeCell ref="B1054:N1054"/>
+    <mergeCell ref="C862:N862"/>
+    <mergeCell ref="C600:N600"/>
+    <mergeCell ref="B599:N599"/>
+    <mergeCell ref="C721:N721"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="B527:N527"/>
+    <mergeCell ref="B123:N123"/>
+    <mergeCell ref="C630:N630"/>
+    <mergeCell ref="A628:N628"/>
+    <mergeCell ref="B629:N629"/>
+    <mergeCell ref="B35:N35"/>
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="C312:N312"/>
+    <mergeCell ref="C360:N360"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="C171:N171"/>
+    <mergeCell ref="C124:N124"/>
     <mergeCell ref="B1137:N1137"/>
     <mergeCell ref="C528:N528"/>
     <mergeCell ref="B70:N70"/>
@@ -50717,31 +50741,7 @@
     <mergeCell ref="C834:N834"/>
     <mergeCell ref="C815:N815"/>
     <mergeCell ref="A1053:N1053"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="B527:N527"/>
-    <mergeCell ref="B123:N123"/>
-    <mergeCell ref="C630:N630"/>
-    <mergeCell ref="A628:N628"/>
-    <mergeCell ref="B629:N629"/>
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="B4:N4"/>
-    <mergeCell ref="C312:N312"/>
-    <mergeCell ref="C360:N360"/>
-    <mergeCell ref="A3:N3"/>
     <mergeCell ref="B1003:N1003"/>
-    <mergeCell ref="B1127:N1127"/>
-    <mergeCell ref="A358:N358"/>
-    <mergeCell ref="C198:N198"/>
-    <mergeCell ref="B359:N359"/>
-    <mergeCell ref="A929:N929"/>
-    <mergeCell ref="C1004:N1004"/>
-    <mergeCell ref="B1054:N1054"/>
-    <mergeCell ref="C862:N862"/>
-    <mergeCell ref="C171:N171"/>
-    <mergeCell ref="C600:N600"/>
-    <mergeCell ref="B599:N599"/>
-    <mergeCell ref="C721:N721"/>
-    <mergeCell ref="C124:N124"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -50754,8 +50754,8 @@
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="3" max="3" width="31.5" customWidth="1"/>
+    <col min="4" max="4" width="39.6640625" customWidth="1"/>
     <col min="5" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="30" customWidth="1"/>
@@ -56077,9 +56077,9 @@
       <c r="A224" s="70" t="s">
         <v>1484</v>
       </c>
-      <c r="B224" s="50"/>
-      <c r="C224" s="50"/>
-      <c r="D224" s="51"/>
+      <c r="B224" s="54"/>
+      <c r="C224" s="54"/>
+      <c r="D224" s="55"/>
       <c r="E224" s="1">
         <v>1112</v>
       </c>
@@ -56093,20 +56093,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="A85:H85"/>
-    <mergeCell ref="A213:H213"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A209:H209"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A63:H63"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A161:H161"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A173:H173"/>
-    <mergeCell ref="A111:H111"/>
-    <mergeCell ref="A39:H39"/>
     <mergeCell ref="A224:D224"/>
     <mergeCell ref="A45:H45"/>
     <mergeCell ref="A1:H1"/>
@@ -56122,6 +56108,20 @@
     <mergeCell ref="A128:H128"/>
     <mergeCell ref="A74:H74"/>
     <mergeCell ref="A145:H145"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A85:H85"/>
+    <mergeCell ref="A213:H213"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A209:H209"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A161:H161"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A173:H173"/>
+    <mergeCell ref="A111:H111"/>
+    <mergeCell ref="A39:H39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
